--- a/Result/profitability/2024.xlsx
+++ b/Result/profitability/2024.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05249999999999999</v>
+        <v>0.06749999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>7.94625</v>
+        <v>8.258750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.79</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1525</v>
+        <v>0.15125</v>
       </c>
       <c r="N3" t="n">
-        <v>9.31875</v>
+        <v>9.571249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>0.205</v>
+        <v>0.215</v>
       </c>
       <c r="N4" t="n">
-        <v>10.66625</v>
+        <v>11.0425</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04875000000000002</v>
+        <v>0.07625000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>5.49625</v>
+        <v>6.043750000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.125</v>
+        <v>-0.10375</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.07625</v>
+        <v>-2.259999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.22375</v>
+        <v>-0.22</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.342499999999999</v>
+        <v>-6.104999999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.22125</v>
+        <v>-0.2275</v>
       </c>
       <c r="N8" t="n">
-        <v>-6.46375</v>
+        <v>-6.166249999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.2425</v>
       </c>
       <c r="N9" t="n">
-        <v>-6.39375</v>
+        <v>-6.393749999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>-0.2375</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.42625</v>
+        <v>-6.426249999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.27875</v>
       </c>
       <c r="N11" t="n">
-        <v>-7.05875</v>
+        <v>-7.058749999999998</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.31875</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.970000000000001</v>
+        <v>-7.969999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>277</v>
+      </c>
+      <c r="D75" t="n">
+        <v>247</v>
+      </c>
+      <c r="E75" t="n">
+        <v>30</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.20%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.03999999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3125</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.380000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2843488649940265</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6875981161695448</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
